--- a/artfynd/A 38400-2021 artfynd.xlsx
+++ b/artfynd/A 38400-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38400-2021 artfynd.xlsx
+++ b/artfynd/A 38400-2021 artfynd.xlsx
@@ -970,7 +970,7 @@
         <v>120849672</v>
       </c>
       <c r="B4" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 38400-2021 artfynd.xlsx
+++ b/artfynd/A 38400-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>62276269</v>
       </c>
       <c r="B2" t="n">
-        <v>12255</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750210.4972813188</v>
+        <v>750210</v>
       </c>
       <c r="R2" t="n">
-        <v>7090338.237909908</v>
+        <v>7090338</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -769,19 +764,9 @@
           <t>2014-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -817,76 +802,56 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marja Fors, Roger Mugerwa Pettersson</t>
+          <t>Roger Mugerwa Pettersson, Marja Fors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62309312</v>
+        <v>93600374</v>
       </c>
       <c r="B3" t="n">
-        <v>6912</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105389</v>
+        <v>232272</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epuraea oblonga</t>
+          <t>Sarcoscypha austriaca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Herbst, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klabböle, Vb</t>
+          <t>Umeå Kvarnsvedjan, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750210.4972813188</v>
+        <v>750170</v>
       </c>
       <c r="R3" t="n">
-        <v>7090338.237909908</v>
+        <v>7090445</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,27 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>trädfönster 160S = sälg</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,134 +892,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sälg i lövskog</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Roger Mugerwa Pettersson</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Mugerwa Pettersson</t>
+          <t>Gunhild Eriksson Nyberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marja Fors, Roger Mugerwa Pettersson</t>
+          <t>Gunhild Eriksson Nyberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>120849672</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90715</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Klabberget, Vb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>750220</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7090528</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-09-24</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Sweco naturvärdesinventering och artinventering</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
